--- a/data/trans_camb/P1428-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1428-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-1,69</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,75</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 2,03</t>
+          <t>-3,42; 2,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,45</t>
+          <t>-5,39; -0,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,04</t>
+          <t>-3,15; 1,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -0,11</t>
+          <t>-8,99; -0,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,74; -0,33</t>
+          <t>-8,72; -0,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 2,09</t>
+          <t>-6,18; 2,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,25</t>
+          <t>-4,82; 0,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -0,94</t>
+          <t>-5,44; -1,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,49</t>
+          <t>-3,15; 1,44</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-11,3%</t>
+          <t>-13,69%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-19,1%</t>
+          <t>-17,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-11,55%</t>
+          <t>-11,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,85; 63,65</t>
+          <t>-58,99; 72,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,42; -6,34</t>
+          <t>-84,6; 7,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,46; 66,54</t>
+          <t>-52,01; 58,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,8; 1,91</t>
+          <t>-74,08; 0,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,16; 1,5</t>
+          <t>-72,39; 0,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 31,44</t>
+          <t>-48,06; 27,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,21; 7,39</t>
+          <t>-59,46; 6,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,68; -15,77</t>
+          <t>-70,08; -17,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 32,0</t>
+          <t>-38,38; 27,25</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,94</t>
+          <t>-2,83; 2,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 1,76</t>
+          <t>-3,66; 1,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,75</t>
+          <t>-2,71; 2,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,84</t>
+          <t>-5,39; 1,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,89</t>
+          <t>-5,8; 0,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 7,58</t>
+          <t>0,79; 7,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,6</t>
+          <t>-3,34; 1,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,49</t>
+          <t>-4,02; 0,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,29</t>
+          <t>-0,3; 4,1</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,45; 127,25</t>
+          <t>-54,95; 119,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,52; 85,27</t>
+          <t>-67,04; 89,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,48; 117,29</t>
+          <t>-46,72; 97,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,57; 47,44</t>
+          <t>-65,23; 39,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,31; 23,5</t>
+          <t>-70,09; 28,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 171,27</t>
+          <t>8,88; 185,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 42,87</t>
+          <t>-52,26; 32,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,61; 17,61</t>
+          <t>-63,8; 11,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 113,33</t>
+          <t>-5,56; 104,6</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,81</t>
+          <t>-3,69</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>-1,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 3,67</t>
+          <t>-2,78; 3,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -1,14</t>
+          <t>-6,2; -1,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 0,46</t>
+          <t>-4,05; 1,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 2,56</t>
+          <t>-12,7; 3,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 3,62</t>
+          <t>-13,94; 3,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 4,22</t>
+          <t>-11,47; 4,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,54</t>
+          <t>-3,6; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -0,89</t>
+          <t>-6,78; -0,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 0,11</t>
+          <t>-4,34; 1,84</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-42,6%</t>
+          <t>-15,53%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-19,51%</t>
+          <t>-18,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-36,07%</t>
+          <t>-12,08%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 67,38</t>
+          <t>-31,79; 63,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,39; -17,12</t>
+          <t>-73,29; -15,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,18; 7,69</t>
+          <t>-48,68; 30,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,51; 21,15</t>
+          <t>-51,54; 27,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,3; 25,44</t>
+          <t>-58,48; 20,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,51; 27,69</t>
+          <t>-46,59; 30,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,22; 30,6</t>
+          <t>-30,19; 26,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,35; -7,89</t>
+          <t>-60,42; -10,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,88; 0,2</t>
+          <t>-37,67; 20,93</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,93</t>
+          <t>-3,92</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,82</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,05</t>
+          <t>-3,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -2,67</t>
+          <t>-7,14; -2,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -3,91</t>
+          <t>-8,02; -3,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,05; -1,86</t>
+          <t>-6,31; -1,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -5,07</t>
+          <t>-11,19; -5,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,68; -5,58</t>
+          <t>-11,25; -5,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 48,82</t>
+          <t>-6,4; -0,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,78; -4,39</t>
+          <t>-7,86; -4,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -5,04</t>
+          <t>-8,3; -5,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 31,05</t>
+          <t>-5,24; -1,5</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-37,18%</t>
+          <t>-37,04%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>114,17%</t>
+          <t>-21,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>-27,82%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,39; -27,3</t>
+          <t>-59,96; -28,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-67,64; -40,4</t>
+          <t>-67,3; -39,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,99; -20,54</t>
+          <t>-51,99; -20,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-71,97; -41,43</t>
+          <t>-71,36; -42,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,36; -44,97</t>
+          <t>-72,64; -44,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 384,45</t>
+          <t>-39,95; -2,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-60,87; -39,98</t>
+          <t>-61,23; -38,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,94; -45,88</t>
+          <t>-65,77; -46,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 271,81</t>
+          <t>-40,19; -13,48</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,59</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 0,34</t>
+          <t>-6,69; 0,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -0,55</t>
+          <t>-7,06; -0,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,07</t>
+          <t>-5,96; 0,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 0,89</t>
+          <t>-7,47; 0,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,52; -1,29</t>
+          <t>-9,67; -1,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 4,28</t>
+          <t>-3,04; 4,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,06; -0,27</t>
+          <t>-6,16; -0,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -2,2</t>
+          <t>-8,02; -2,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 2,82</t>
+          <t>-3,52; 2,25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-16,57%</t>
+          <t>-26,57%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,26%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-2,34%</t>
+          <t>-4,13%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,3; 5,41</t>
+          <t>-63,34; 8,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-64,07; -7,68</t>
+          <t>-66,25; -5,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,55; 32,07</t>
+          <t>-53,86; 14,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 6,26</t>
+          <t>-36,52; 6,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-47,2; -8,24</t>
+          <t>-47,17; -9,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 27,0</t>
+          <t>-14,35; 30,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-38,02; -2,25</t>
+          <t>-38,79; -3,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,83; -18,98</t>
+          <t>-50,87; -20,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 22,16</t>
+          <t>-21,85; 17,98</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,26</t>
+          <t>-5,67</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,26</t>
+          <t>-5,18</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,24</t>
+          <t>-0,97; 3,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,76; -0,26</t>
+          <t>-2,78; -0,26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,52</t>
+          <t>-1,82; 0,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -2,02</t>
+          <t>-9,12; -2,09</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -8,7</t>
+          <t>-15,05; -8,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,33; -1,71</t>
+          <t>-9,12; -2,32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,96; -1,11</t>
+          <t>-7,04; -1,41</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,02; -7,61</t>
+          <t>-12,68; -7,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -2,56</t>
+          <t>-7,88; -2,44</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-52,78%</t>
+          <t>-51,59%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-21,08%</t>
+          <t>-22,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-25,89%</t>
+          <t>-25,51%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-33,23; -8,77</t>
+          <t>-34,29; -8,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-57,34; -36,37</t>
+          <t>-57,0; -37,71</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-31,72; -7,77</t>
+          <t>-34,21; -9,92</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,43; -5,89</t>
+          <t>-32,67; -7,43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-60,1; -39,68</t>
+          <t>-58,33; -39,09</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-37,29; -13,48</t>
+          <t>-36,29; -13,07</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-2,22</t>
+          <t>-1,99</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>-3,25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-2,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,32; -0,89</t>
+          <t>-3,32; -0,97</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,81; -2,58</t>
+          <t>-4,74; -2,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,66; -1,08</t>
+          <t>-3,17; -0,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,03; -3,45</t>
+          <t>-6,99; -3,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -6,6</t>
+          <t>-9,9; -6,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 17,66</t>
+          <t>-4,79; -1,69</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,78; -2,61</t>
+          <t>-4,77; -2,52</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,02; -4,91</t>
+          <t>-7,1; -4,98</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 8,99</t>
+          <t>-3,64; -1,62</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-30,65%</t>
+          <t>-27,54%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>-18,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-1,53%</t>
+          <t>-20,61%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-41,75; -13,03</t>
+          <t>-42,55; -13,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,97; -37,36</t>
+          <t>-60,29; -38,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-47,62; -16,07</t>
+          <t>-39,77; -12,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,71; -20,54</t>
+          <t>-37,5; -20,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,78; -38,9</t>
+          <t>-53,4; -39,72</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 102,19</t>
+          <t>-25,72; -10,0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-36,31; -21,67</t>
+          <t>-36,35; -21,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-53,46; -40,76</t>
+          <t>-54,07; -41,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 72,65</t>
+          <t>-27,52; -13,78</t>
         </is>
       </c>
     </row>
